--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260828.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260828.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>42,920,027</t>
+          <t>42,828,027</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>64.53%</t>
+          <t>64.20%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2,591,703</t>
+          <t>2,586,703</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>6.38%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>21,497,000</t>
+          <t>21,451,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.36%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,841,267</t>
+          <t>5,828,267</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
@@ -699,56 +699,56 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>512,000</t>
+          <t>511,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2,322,901</t>
+          <t>20,491,286</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>20,535,286</t>
+          <t>2,317,901</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>563,222</t>
+          <t>562,222</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -777,39 +777,39 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,653,285</t>
+          <t>2,766,608</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,772,608</t>
+          <t>4,643,285</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -831,29 +831,29 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>183,515</t>
+          <t>182,515</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>1,188,617</t>
+          <t>165,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>165,000</t>
+          <t>1,185,617</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2,008,288</t>
+          <t>3,436,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,22 +909,22 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>3,443,000</t>
+          <t>2,004,288</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>5,446,296</t>
+          <t>5,434,296</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>5,316,520</t>
+          <t>5,304,520</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -1029,34 +1029,34 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>314,672</t>
+          <t>313,672</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,343,000</t>
+          <t>603,600</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1085,39 +1085,39 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>605,600</t>
+          <t>1,340,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>860,349</t>
+          <t>12,895,134</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,22 +1129,22 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>12,922,134</t>
+          <t>858,349</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,005,822</t>
+          <t>1,003,822</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>811,897</t>
+          <t>2,005,587</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,44 +1217,44 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>580,000</t>
+          <t>809,897</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,009,587</t>
+          <t>578,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>377,000</t>
+          <t>376,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1315,51 +1315,51 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,839,000</t>
+          <t>1,835,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,234,000</t>
+          <t>5,728,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,741,000</t>
+          <t>3,227,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>772,000</t>
+          <t>770,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,201,441</t>
+          <t>1,198,441</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>939,659</t>
+          <t>937,659</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,492,981</t>
+          <t>3,484,981</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>7,194,249</t>
+          <t>4,460,578</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>4,469,578</t>
+          <t>7,178,249</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>10,638,121</t>
+          <t>583,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>584,000</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>10,615,121</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,383,384</t>
+          <t>1,380,384</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,44 +1591,44 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>2,606,703</t>
+          <t>146,386</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>146,386</t>
+          <t>2,600,703</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>391,000</t>
+          <t>390,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>2,198,107</t>
+          <t>2,193,107</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>1,189,076</t>
+          <t>1,187,076</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,39 +1745,39 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>4,977,956</t>
+          <t>777,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>807,000</t>
+          <t>182,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>182,000</t>
+          <t>291,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>779,000</t>
+          <t>228,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>291,000</t>
+          <t>805,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>228,000</t>
+          <t>498,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1,565,400</t>
+          <t>4,966,956</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>499,000</t>
+          <t>320,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>321,000</t>
+          <t>1,562,400</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,006,121</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,764,000</t>
+          <t>1,760,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>1,004,121</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>157,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>332,000</t>
+          <t>157,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>332,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>171,000</t>
+          <t>178,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>178,000</t>
+          <t>681,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>255,000</t>
+          <t>254,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>682,000</t>
+          <t>171,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>72,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>72,000</t>
+          <t>336,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2207,17 +2207,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>337,000</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>214,273,905</t>
+          <t>289,818,293</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>348,782,610</t>
+          <t>352,245,810</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>2,101,924,284</t>
+          <t>1,084,609,073</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>2,068,013,624</t>
+          <t>1,069,670,204</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr"/>
